--- a/02_Zero_Shot/outputs/NLI/Cross-Encoder DeBERTa/RESULT_clap_cross-encoder-deberta_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/Cross-Encoder DeBERTa/RESULT_clap_cross-encoder-deberta_zeroshot.xlsx
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.181462507187833</v>
+        <v>0.1814625071878329</v>
       </c>
     </row>
     <row r="5">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>319.6557068859993</v>
+        <v>410.0259083279998</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1065519022953331</v>
+        <v>0.1366753027759999</v>
       </c>
     </row>
   </sheetData>
